--- a/outputs/pdgm-test-paketi-20260927/H09_IKI_NO_SUTUNU.xlsx
+++ b/outputs/pdgm-test-paketi-20260927/H09_IKI_NO_SUTUNU.xlsx
@@ -10646,7 +10646,11 @@
       <c r="V293" s="9" t="n"/>
       <c r="W293" s="10" t="n"/>
       <c r="X293" s="10" t="n"/>
-      <c r="Y293" s="9" t="n"/>
+      <c r="Y293" s="9" t="inlineStr">
+        <is>
+          <t>PLANA ALINDI</t>
+        </is>
+      </c>
       <c r="Z293" s="9" t="n"/>
     </row>
     <row r="294">
@@ -11998,11 +12002,7 @@
         <v>46300</v>
       </c>
       <c r="X311" s="10" t="n"/>
-      <c r="Y311" s="9" t="inlineStr">
-        <is>
-          <t>DİZGİDE</t>
-        </is>
-      </c>
+      <c r="Y311" s="9" t="n"/>
       <c r="Z311" s="9" t="inlineStr">
         <is>
           <t>VAR</t>
@@ -15634,7 +15634,7 @@
       <c r="U78" s="18" t="n"/>
       <c r="V78" s="17" t="inlineStr">
         <is>
-          <t>DİZGİDE</t>
+          <t>MALZEME TEDARİK</t>
         </is>
       </c>
       <c r="W78" s="17" t="n"/>
